--- a/giapha.xlsx
+++ b/giapha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAILIEU\Thinh\Gia pha\Ho Bui\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA37EA6-C022-40B8-812F-8CA23DC11AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECDFF62-F2F9-4C18-B2C6-74A7FC4EC207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
   <si>
     <t>ID</t>
   </si>
@@ -251,13 +250,22 @@
   </si>
   <si>
     <t>Bùi Minh Toàn</t>
+  </si>
+  <si>
+    <t>Bùi Đức Kiên</t>
+  </si>
+  <si>
+    <t>Bùi Đắc Kha</t>
+  </si>
+  <si>
+    <t>Bùi Đăng Duy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,6 +298,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF081B3A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -311,7 +325,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -377,11 +391,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -389,9 +427,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -428,21 +463,29 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -723,295 +766,295 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="6"/>
-    <col min="2" max="2" width="26.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="16" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18" style="6" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" style="6" customWidth="1"/>
-    <col min="8" max="8" width="18" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="9.140625" style="5"/>
+    <col min="2" max="2" width="26.5703125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="16" style="5" customWidth="1"/>
+    <col min="6" max="6" width="18" style="5" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="18" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>0</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>1</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>18257</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11" t="s">
+      <c r="G2" s="9"/>
+      <c r="H2" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>1</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>2</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="12" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>2</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>3</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>25386</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="9"/>
+      <c r="H4" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <v>2</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>3</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>3</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>4</v>
       </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
       <c r="H6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>3</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>4</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
       <c r="H7" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>3</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>4</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
       <c r="H8" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>3</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>4</v>
       </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
       <c r="H9" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>3</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>4</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17" t="s">
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>3</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>4</v>
       </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>3</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>4</v>
       </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="13">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>3</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>4</v>
       </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17" t="s">
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="6">
         <v>3</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="6">
         <v>4</v>
       </c>
       <c r="E14" s="16"/>
@@ -1021,599 +1064,671 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="24">
         <v>4</v>
       </c>
-      <c r="D15" s="21">
-        <v>5</v>
-      </c>
-      <c r="H15" s="6" t="s">
+      <c r="D15" s="24">
+        <v>5</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13">
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="24">
         <v>4</v>
       </c>
-      <c r="D16" s="21">
-        <v>5</v>
-      </c>
-      <c r="H16" s="6" t="s">
+      <c r="D16" s="24">
+        <v>5</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="13">
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="24">
         <v>4</v>
       </c>
-      <c r="D17" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
+      <c r="D17" s="24">
+        <v>5</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="24">
         <v>4</v>
       </c>
-      <c r="D18" s="21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="13">
+      <c r="D18" s="24">
+        <v>5</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="24">
         <v>4</v>
       </c>
-      <c r="D19" s="21">
-        <v>5</v>
-      </c>
+      <c r="D19" s="24">
+        <v>5</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
+      <c r="A20" s="20">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="22">
         <v>8</v>
       </c>
-      <c r="D20" s="7">
-        <v>5</v>
-      </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
+      <c r="D20" s="22">
+        <v>5</v>
+      </c>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="6">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="6">
         <v>8</v>
       </c>
-      <c r="D21" s="7">
-        <v>5</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
+      <c r="D21" s="6">
+        <v>5</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="13">
+      <c r="A22" s="12">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="6">
         <v>8</v>
       </c>
-      <c r="D22" s="7">
-        <v>5</v>
-      </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
+      <c r="D22" s="6">
+        <v>5</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="13">
+      <c r="A23" s="12">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="6">
         <v>8</v>
       </c>
-      <c r="D23" s="7">
-        <v>5</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
+      <c r="D23" s="6">
+        <v>5</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="6">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="6">
         <v>8</v>
       </c>
-      <c r="D24" s="7">
-        <v>5</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
+      <c r="D24" s="6">
+        <v>5</v>
+      </c>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="13">
+      <c r="A25" s="12">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="6">
         <v>8</v>
       </c>
-      <c r="D25" s="7">
-        <v>5</v>
-      </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17" t="s">
+      <c r="D25" s="6">
+        <v>5</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
+      <c r="A26" s="12">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="6">
         <v>9</v>
       </c>
-      <c r="D26" s="7">
-        <v>5</v>
-      </c>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17" t="s">
+      <c r="D26" s="6">
+        <v>5</v>
+      </c>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="6">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="6">
         <v>9</v>
       </c>
-      <c r="D27" s="7">
-        <v>5</v>
-      </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17" t="s">
+      <c r="D27" s="6">
+        <v>5</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="13">
+      <c r="A28" s="12">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="6">
         <v>12</v>
       </c>
-      <c r="D28" s="7">
-        <v>5</v>
-      </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17" t="s">
+      <c r="D28" s="6">
+        <v>5</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="13">
+      <c r="A29" s="12">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="6">
         <v>12</v>
       </c>
-      <c r="D29" s="7">
-        <v>5</v>
-      </c>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17" t="s">
+      <c r="D29" s="6">
+        <v>5</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30" s="6">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="6">
         <v>13</v>
       </c>
-      <c r="D30" s="7">
-        <v>5</v>
-      </c>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17" t="s">
+      <c r="D30" s="6">
+        <v>5</v>
+      </c>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="13">
+      <c r="A31" s="12">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="6">
         <v>13</v>
       </c>
-      <c r="D31" s="7">
-        <v>5</v>
-      </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
+      <c r="D31" s="6">
+        <v>5</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="13">
+      <c r="A32" s="12">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="6">
         <v>13</v>
       </c>
-      <c r="D32" s="7">
-        <v>5</v>
-      </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17" t="s">
+      <c r="D32" s="6">
+        <v>5</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="13">
+      <c r="A33" s="12">
         <v>32</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="6">
         <v>14</v>
       </c>
-      <c r="D33" s="7">
-        <v>5</v>
-      </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
+      <c r="D33" s="6">
+        <v>5</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="13">
+      <c r="A34" s="12">
         <v>33</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="6">
         <v>15</v>
       </c>
-      <c r="D34" s="7">
-        <v>5</v>
-      </c>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
+      <c r="D34" s="6">
+        <v>5</v>
+      </c>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
     </row>
     <row r="35" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7">
+      <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>16</v>
       </c>
-      <c r="D35" s="7">
-        <v>5</v>
-      </c>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
+      <c r="D35" s="6">
+        <v>5</v>
+      </c>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="13">
+      <c r="A36" s="12">
         <v>35</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="6">
         <v>16</v>
       </c>
-      <c r="D36" s="7">
-        <v>5</v>
-      </c>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
+      <c r="D36" s="6">
+        <v>5</v>
+      </c>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="13">
+      <c r="A37" s="12">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="6">
         <v>24</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="6">
         <v>6</v>
       </c>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="13">
+      <c r="A38" s="12">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="6">
         <v>24</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="6">
         <v>6</v>
       </c>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="13">
+      <c r="A39" s="12">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="6">
         <v>24</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="6">
         <v>6</v>
       </c>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="A40" s="6">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="6">
         <v>27</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="6">
         <v>6</v>
       </c>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="13">
+      <c r="A41" s="12">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="6">
         <v>27</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="6">
         <v>6</v>
       </c>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="13">
+      <c r="A42" s="12">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="6">
         <v>28</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="6">
         <v>6</v>
       </c>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="13">
+      <c r="A43" s="12">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="6">
         <v>29</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="6">
         <v>6</v>
       </c>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="13">
+      <c r="A44" s="12">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="6">
         <v>29</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="6">
         <v>6</v>
       </c>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
+      <c r="A45" s="6">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="6">
         <v>31</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="6">
         <v>6</v>
       </c>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="13">
+      <c r="A46" s="12">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="6">
         <v>31</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="6">
         <v>6</v>
       </c>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="13">
+      <c r="A47" s="12">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="6">
         <v>31</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="6">
         <v>6</v>
       </c>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+    </row>
+    <row r="48" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A48" s="6">
+        <v>47</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" s="24">
+        <v>34</v>
+      </c>
+      <c r="D48" s="24">
+        <v>6</v>
+      </c>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+    </row>
+    <row r="49" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="6">
+        <v>48</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="24">
+        <v>34</v>
+      </c>
+      <c r="D49" s="24">
+        <v>6</v>
+      </c>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+    </row>
+    <row r="50" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A50" s="6">
+        <v>49</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="24">
+        <v>35</v>
+      </c>
+      <c r="D50" s="24">
+        <v>6</v>
+      </c>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
